--- a/tame_output/ON/bt/strategyON_20240113.xlsx
+++ b/tame_output/ON/bt/strategyON_20240113.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>1.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.6%</t>
+          <t>452.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.8%</t>
+          <t>101.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-155.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.0%</t>
+          <t>131.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-01-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.5%</t>
+          <t>124.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>2.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1840"/>
+  <dimension ref="A1:G1841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.370022263565001</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43881,6 +43881,29 @@
       </c>
       <c r="G1840" t="n">
         <v>4.49779191713359</v>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" s="2" t="n">
+        <v>45303</v>
+      </c>
+      <c r="B1841" t="n">
+        <v>3.298466227775266</v>
+      </c>
+      <c r="C1841" t="n">
+        <v>3.13483507841956</v>
+      </c>
+      <c r="D1841" t="n">
+        <v>1.639253495930899</v>
+      </c>
+      <c r="E1841" t="n">
+        <v>3.790180052478172</v>
+      </c>
+      <c r="F1841" t="n">
+        <v>2.241866401647637</v>
+      </c>
+      <c r="G1841" t="n">
+        <v>4.479954919408142</v>
       </c>
     </row>
   </sheetData>
